--- a/片仮名（かたかな）/片假名.xlsx
+++ b/片仮名（かたかな）/片假名.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F159740-57FB-4F1C-920B-91C956B0C752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="3" r:id="rId1"/>
@@ -907,6 +907,7 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -922,7 +923,6 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1623,7 +1623,7 @@
       <c r="B4" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="18" t="s">
         <v>35</v>
       </c>
       <c r="D4" s="10" t="s">
@@ -1632,7 +1632,7 @@
       <c r="E4" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="18" t="s">
         <v>38</v>
       </c>
       <c r="N4" s="9" t="s">
@@ -1658,7 +1658,7 @@
       <c r="C5" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="18" t="s">
         <v>41</v>
       </c>
       <c r="E5" s="10" t="s">
@@ -1811,17 +1811,17 @@
         <v>58</v>
       </c>
       <c r="C9" s="11"/>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="18" t="s">
         <v>59</v>
       </c>
       <c r="E9" s="11"/>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="18" t="s">
         <v>60</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J9" s="19" t="s">
         <v>83</v>
       </c>
       <c r="N9" s="9" t="s">
@@ -1850,7 +1850,7 @@
       <c r="F10" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="19"/>
+      <c r="J10" s="20"/>
       <c r="K10" s="9" t="s">
         <v>96</v>
       </c>
@@ -1880,10 +1880,10 @@
       <c r="F11" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="J11" s="20" t="s">
+      <c r="J11" s="21" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1891,8 +1891,8 @@
       <c r="B12" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="I12" s="19"/>
-      <c r="J12" s="21"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="22"/>
       <c r="K12" s="9" t="s">
         <v>97</v>
       </c>
@@ -1902,19 +1902,19 @@
       <c r="C13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
-      <c r="H13" s="18" t="s">
+      <c r="H13" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="J13" s="22" t="s">
+      <c r="J13" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="K13" s="18" t="s">
+      <c r="K13" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="L13" s="18" t="s">
+      <c r="L13" s="19" t="s">
         <v>86</v>
       </c>
       <c r="M13" t="s">
@@ -1940,11 +1940,11 @@
       <c r="F14" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="20"/>
       <c r="M14" s="9" t="s">
         <v>94</v>
       </c>
@@ -1961,7 +1961,7 @@
       <c r="F15" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="20" t="s">
+      <c r="J15" s="21" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       <c r="E16" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="J16" s="21"/>
+      <c r="J16" s="22"/>
     </row>
     <row r="17" spans="2:11" ht="18" x14ac:dyDescent="0.45">
       <c r="F17" s="9" t="s">
@@ -2109,15 +2109,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="I13:I14"/>
     <mergeCell ref="H13:H14"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="J13:J14"/>
     <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="I13:I14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
